--- a/PCB/Build_2027.xlsx
+++ b/PCB/Build_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitRepos\QUTstevenbulmer\Unit_EGB220\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57C83DF-B831-4174-98B2-76BE3CF7517E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8B6FD4-638D-4815-B438-CF67193189EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EE1CEB4E-5DC4-4AEE-A762-D263ECD2BF91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE1CEB4E-5DC4-4AEE-A762-D263ECD2BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="2" r:id="rId1"/>
@@ -1504,7 +1504,7 @@
         <v>150</v>
       </c>
       <c r="E7">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1525,11 +1525,11 @@
       </c>
       <c r="P7">
         <f>E7*(L7+SUM(G7:I7))</f>
-        <v>7181.0249999999996</v>
+        <v>10053.434999999999</v>
       </c>
       <c r="R7">
         <f>E7*(N7+SUM(G7:I7))</f>
-        <v>5825.6812499999996</v>
+        <v>8155.9537499999997</v>
       </c>
     </row>
     <row r="9" spans="3:20" x14ac:dyDescent="0.25">
@@ -1549,31 +1549,31 @@
         <v>2</v>
       </c>
       <c r="L9">
-        <f>Build_2027!P36</f>
-        <v>0</v>
+        <f>Build_2027!U31</f>
+        <v>0.97040000000000004</v>
       </c>
       <c r="N9">
-        <f>Build_2027!Q36</f>
-        <v>0</v>
+        <f>Build_2027!V31</f>
+        <v>0.8052999999999999</v>
       </c>
       <c r="P9">
         <f>E9*(L9+SUM(G9:I9))</f>
-        <v>1700</v>
+        <v>1797.0400000000002</v>
       </c>
       <c r="R9">
         <f>E9*(N9+SUM(G9:I9))</f>
-        <v>1700</v>
+        <v>1780.53</v>
       </c>
     </row>
     <row r="14" spans="3:20" x14ac:dyDescent="0.25">
       <c r="P14" s="1">
         <f>SUM(P7:P13)</f>
-        <v>8881.0249999999996</v>
+        <v>11850.475</v>
       </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1">
         <f>SUM(R7:R13)</f>
-        <v>7525.6812499999996</v>
+        <v>9936.4837499999994</v>
       </c>
       <c r="S14" s="3"/>
       <c r="T14" s="1" t="s">
